--- a/output/pdf_financials_xlsx/DRY.xlsx
+++ b/output/pdf_financials_xlsx/DRY.xlsx
@@ -672,16 +672,16 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000412</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.084456</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.121083</v>
       </c>
     </row>
     <row r="13">
@@ -1024,16 +1024,16 @@
         <v>-0.032659</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.282441</v>
+        <v>-0.282853</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-3.76986</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.734862</v>
+        <v>-3.819318</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-8.320339000000001</v>
+        <v>-8.441421999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1068,16 +1068,16 @@
         <v>-0.032659</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.282441</v>
+        <v>-0.282853</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-3.76986</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.734862</v>
+        <v>-3.819318</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-8.320339000000001</v>
+        <v>-8.441421999999999</v>
       </c>
     </row>
     <row r="30">
@@ -3224,10 +3224,10 @@
         <v>0</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.003037</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.406904</v>
       </c>
     </row>
     <row r="125">
@@ -3248,10 +3248,10 @@
         <v>0</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.003037</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.406904</v>
       </c>
     </row>
     <row r="126">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -6153,7 +6153,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -6467,7 +6471,11 @@
           <t>Leae payments</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -8039,7 +8047,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -8080,7 +8088,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -8523,7 +8531,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">

--- a/output/pdf_financials_xlsx/DRY.xlsx
+++ b/output/pdf_financials_xlsx/DRY.xlsx
@@ -1923,16 +1923,16 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.0225</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="68">
@@ -2664,10 +2664,8 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>-0.001475</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>-0.005265</v>
@@ -2679,7 +2677,7 @@
         <v>0.019046</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>-0.959008</v>
       </c>
     </row>
     <row r="102">
@@ -2783,7 +2781,7 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.005069</v>
+        <v>0.003594</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>0.019541</v>
@@ -2795,7 +2793,7 @@
         <v>-0.300617</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-0.295683</v>
+        <v>-1.254691</v>
       </c>
     </row>
     <row r="107">
@@ -5722,7 +5720,11 @@
           <t>GST Receivable</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -7205,7 +7207,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E92" s="5" t="n">
         <v>-0.001475</v>
       </c>
